--- a/Airlines-Services/airlines/management/commands/AirlineRoutesWayPoints/AirlineRoute-LPFR-EBBR.xlsx
+++ b/Airlines-Services/airlines/management/commands/AirlineRoutesWayPoints/AirlineRoute-LPFR-EBBR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rober\git\flight-profile\airline\management\commands\AirlineRoutesWayPoints\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rober\git\Airlines-Services\Airlines-Services\airlines\management\commands\AirlineRoutesWayPoints\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA3ACCA-EE54-4639-8E06-26D1E0641CA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{021C0F53-D318-4289-BFEA-87BCE72C692A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61E0CD33-709C-40FB-8210-48522662BDB4}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{61E0CD33-709C-40FB-8210-48522662BDB4}"/>
   </bookViews>
   <sheets>
     <sheet name="WayPoints" sheetId="1" r:id="rId1"/>
@@ -125,180 +125,6 @@
     <t>ARVOL</t>
   </si>
   <si>
-    <t>N37°00\'48.99"</t>
-  </si>
-  <si>
-    <t>W007°58\'30.00"</t>
-  </si>
-  <si>
-    <t>N37°07\'43.99"</t>
-  </si>
-  <si>
-    <t>W007°22\'59.99"</t>
-  </si>
-  <si>
-    <t>N37°09\'54.99"</t>
-  </si>
-  <si>
-    <t>W007°11\'30.99"</t>
-  </si>
-  <si>
-    <t>N37°57\'00.00"</t>
-  </si>
-  <si>
-    <t>W006°00\'00.00"</t>
-  </si>
-  <si>
-    <t>N38°35\'49.99"</t>
-  </si>
-  <si>
-    <t>W005°28\'36.99"</t>
-  </si>
-  <si>
-    <t>N39°00\'00.00"</t>
-  </si>
-  <si>
-    <t>W005°09\'00.00"</t>
-  </si>
-  <si>
-    <t>N39°58\'09.99"</t>
-  </si>
-  <si>
-    <t>W004°20\'15.00"</t>
-  </si>
-  <si>
-    <t>N41°09\'05.99"</t>
-  </si>
-  <si>
-    <t>W003°36\'16.99"</t>
-  </si>
-  <si>
-    <t>N41°30\'15.00"</t>
-  </si>
-  <si>
-    <t>W003°24\'41.99"</t>
-  </si>
-  <si>
-    <t>N42°27\'11.99"</t>
-  </si>
-  <si>
-    <t>W002°52\'51.00"</t>
-  </si>
-  <si>
-    <t>N43°38\'47.00"</t>
-  </si>
-  <si>
-    <t>W001°57\'44.99"</t>
-  </si>
-  <si>
-    <t>N45°02\'39.99"</t>
-  </si>
-  <si>
-    <t>W001°02\'22.99"</t>
-  </si>
-  <si>
-    <t>N45°11\'44.99"</t>
-  </si>
-  <si>
-    <t>W000°51\'42.00"</t>
-  </si>
-  <si>
-    <t>N46°34\'52.00"</t>
-  </si>
-  <si>
-    <t>E000°17\'52.99"</t>
-  </si>
-  <si>
-    <t>N47°02\'48.99"</t>
-  </si>
-  <si>
-    <t>E000°41\'30.00"</t>
-  </si>
-  <si>
-    <t>N47°29\'43.99"</t>
-  </si>
-  <si>
-    <t>E000°44\'18.99"</t>
-  </si>
-  <si>
-    <t>N47°50\'14.00"</t>
-  </si>
-  <si>
-    <t>E000°54\'26.00"</t>
-  </si>
-  <si>
-    <t>N48°12\'54.00"</t>
-  </si>
-  <si>
-    <t>E001°05\'55.99"</t>
-  </si>
-  <si>
-    <t>N48°33\'01.99"</t>
-  </si>
-  <si>
-    <t>E001°16\'14.99"</t>
-  </si>
-  <si>
-    <t>N48°58\'30.99"</t>
-  </si>
-  <si>
-    <t>E001°29\'10.00"</t>
-  </si>
-  <si>
-    <t>N49°21\'03.00"</t>
-  </si>
-  <si>
-    <t>E002°08\'03.00"</t>
-  </si>
-  <si>
-    <t>N49°30\'50.99"</t>
-  </si>
-  <si>
-    <t>E002°25\'17.00"</t>
-  </si>
-  <si>
-    <t>N49°33\'09.99"</t>
-  </si>
-  <si>
-    <t>E002°29\'22.00"</t>
-  </si>
-  <si>
-    <t>N49°49\'33.99"</t>
-  </si>
-  <si>
-    <t>E002°45\'18.99"</t>
-  </si>
-  <si>
-    <t>N49°54\'45.00"</t>
-  </si>
-  <si>
-    <t>E002°50\'23.99"</t>
-  </si>
-  <si>
-    <t>N50°00\'00.00"</t>
-  </si>
-  <si>
-    <t>E002°55\'31.99"</t>
-  </si>
-  <si>
-    <t>N50°13\'41.00"</t>
-  </si>
-  <si>
-    <t>E003°09\'05.00"</t>
-  </si>
-  <si>
-    <t>N50°24\'14.99"</t>
-  </si>
-  <si>
-    <t>E003°16\'29.99"</t>
-  </si>
-  <si>
-    <t>N50°32\'45.00"</t>
-  </si>
-  <si>
-    <t>E003°29\'48.99"</t>
-  </si>
-  <si>
     <t>order</t>
   </si>
   <si>
@@ -309,6 +135,180 @@
   </si>
   <si>
     <t>longitude</t>
+  </si>
+  <si>
+    <t>N37°00'48.99"</t>
+  </si>
+  <si>
+    <t>N37°07'43.99"</t>
+  </si>
+  <si>
+    <t>N37°09'54.99"</t>
+  </si>
+  <si>
+    <t>N37°57'00.00"</t>
+  </si>
+  <si>
+    <t>N38°35'49.99"</t>
+  </si>
+  <si>
+    <t>N39°00'00.00"</t>
+  </si>
+  <si>
+    <t>N39°58'09.99"</t>
+  </si>
+  <si>
+    <t>N41°09'05.99"</t>
+  </si>
+  <si>
+    <t>N41°30'15.00"</t>
+  </si>
+  <si>
+    <t>N42°27'11.99"</t>
+  </si>
+  <si>
+    <t>N43°38'47.00"</t>
+  </si>
+  <si>
+    <t>N45°02'39.99"</t>
+  </si>
+  <si>
+    <t>N45°11'44.99"</t>
+  </si>
+  <si>
+    <t>N46°34'52.00"</t>
+  </si>
+  <si>
+    <t>N47°02'48.99"</t>
+  </si>
+  <si>
+    <t>N47°29'43.99"</t>
+  </si>
+  <si>
+    <t>N47°50'14.00"</t>
+  </si>
+  <si>
+    <t>N48°12'54.00"</t>
+  </si>
+  <si>
+    <t>N48°33'01.99"</t>
+  </si>
+  <si>
+    <t>N48°58'30.99"</t>
+  </si>
+  <si>
+    <t>N49°21'03.00"</t>
+  </si>
+  <si>
+    <t>N49°30'50.99"</t>
+  </si>
+  <si>
+    <t>N49°33'09.99"</t>
+  </si>
+  <si>
+    <t>N49°49'33.99"</t>
+  </si>
+  <si>
+    <t>N49°54'45.00"</t>
+  </si>
+  <si>
+    <t>N50°00'00.00"</t>
+  </si>
+  <si>
+    <t>N50°13'41.00"</t>
+  </si>
+  <si>
+    <t>N50°24'14.99"</t>
+  </si>
+  <si>
+    <t>N50°32'45.00"</t>
+  </si>
+  <si>
+    <t>W007°58'30.00"</t>
+  </si>
+  <si>
+    <t>W007°22'59.99"</t>
+  </si>
+  <si>
+    <t>W007°11'30.99"</t>
+  </si>
+  <si>
+    <t>W006°00'00.00"</t>
+  </si>
+  <si>
+    <t>W005°28'36.99"</t>
+  </si>
+  <si>
+    <t>W005°09'00.00"</t>
+  </si>
+  <si>
+    <t>W004°20'15.00"</t>
+  </si>
+  <si>
+    <t>W003°36'16.99"</t>
+  </si>
+  <si>
+    <t>W003°24'41.99"</t>
+  </si>
+  <si>
+    <t>W002°52'51.00"</t>
+  </si>
+  <si>
+    <t>W001°57'44.99"</t>
+  </si>
+  <si>
+    <t>W001°02'22.99"</t>
+  </si>
+  <si>
+    <t>W000°51'42.00"</t>
+  </si>
+  <si>
+    <t>E000°17'52.99"</t>
+  </si>
+  <si>
+    <t>E000°41'30.00"</t>
+  </si>
+  <si>
+    <t>E000°44'18.99"</t>
+  </si>
+  <si>
+    <t>E000°54'26.00"</t>
+  </si>
+  <si>
+    <t>E001°05'55.99"</t>
+  </si>
+  <si>
+    <t>E001°16'14.99"</t>
+  </si>
+  <si>
+    <t>E001°29'10.00"</t>
+  </si>
+  <si>
+    <t>E002°08'03.00"</t>
+  </si>
+  <si>
+    <t>E002°25'17.00"</t>
+  </si>
+  <si>
+    <t>E002°29'22.00"</t>
+  </si>
+  <si>
+    <t>E002°45'18.99"</t>
+  </si>
+  <si>
+    <t>E002°50'23.99"</t>
+  </si>
+  <si>
+    <t>E002°55'31.99"</t>
+  </si>
+  <si>
+    <t>E003°09'05.00"</t>
+  </si>
+  <si>
+    <t>E003°16'29.99"</t>
+  </si>
+  <si>
+    <t>E003°29'48.99"</t>
   </si>
 </sst>
 </file>
@@ -692,22 +692,22 @@
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="17.81640625" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
     <col min="4" max="4" width="14.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>88</v>
+        <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>89</v>
+        <v>31</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>90</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -718,10 +718,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -732,10 +732,10 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -746,10 +746,10 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -760,10 +760,10 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -777,7 +777,7 @@
         <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -788,10 +788,10 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -802,10 +802,10 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -816,10 +816,10 @@
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -830,10 +830,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -844,10 +844,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -858,10 +858,10 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -872,10 +872,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -886,10 +886,10 @@
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -900,10 +900,10 @@
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -914,10 +914,10 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -928,10 +928,10 @@
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="D17" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -942,10 +942,10 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="D18" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -956,10 +956,10 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="D19" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -970,10 +970,10 @@
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D20" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -984,10 +984,10 @@
         <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="D21" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -998,10 +998,10 @@
         <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="D22" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1012,10 +1012,10 @@
         <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="D23" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1026,10 +1026,10 @@
         <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="D24" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1040,10 +1040,10 @@
         <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="D25" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1054,10 +1054,10 @@
         <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="D26" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1068,10 +1068,10 @@
         <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="D27" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1082,10 +1082,10 @@
         <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="D28" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1096,10 +1096,10 @@
         <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="D29" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1110,10 +1110,10 @@
         <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="D30" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
